--- a/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92527211313</v>
+        <v>46157.93095709745</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93095709745</v>
+        <v>46157.93356672683</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93356672683</v>
+        <v>46157.93651465011</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93651465011</v>
+        <v>46158.28184631066</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28184631066</v>
+        <v>46158.29762924313</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29762924313</v>
+        <v>46158.29778761211</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29778761211</v>
+        <v>46158.33346085424</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33346085424</v>
+        <v>46158.37204765465</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37204765465</v>
+        <v>46158.37400507963</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
